--- a/documents/shenzhen_air/货物收运检查清单.xlsx
+++ b/documents/shenzhen_air/货物收运检查清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>托运人/托运人代理人检查结果【货物/邮件无隐含性危险品及航空禁运限运物品】
                                                                       检查人：</t>
     </r>
@@ -268,11 +274,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
   <fonts count="35">
     <font>
@@ -510,12 +517,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1312,7 +1319,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1974,10 +1981,7 @@
       <c r="R4" s="11"/>
       <c r="S4" s="11"/>
       <c r="T4" s="11"/>
-      <c r="U4" s="12" t="str">
-        <f ca="1">TEXT(TODAY(),"yyyy年mm月dd日")&amp;""</f>
-        <v>2026年03月05日</v>
-      </c>
+      <c r="U4" s="12"/>
       <c r="V4" s="12"/>
       <c r="W4" s="12"/>
       <c r="X4" s="12"/>

--- a/documents/shenzhen_air/货物收运检查清单.xlsx
+++ b/documents/shenzhen_air/货物收运检查清单.xlsx
@@ -26,60 +26,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>陈志超</author>
-  </authors>
-  <commentList>
-    <comment ref="E15" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-由参数配置输入</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A25" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>陈志超:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-由参数配置输入</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="46">
   <si>
@@ -215,26 +161,8 @@
     <t>未含有航空禁运的物品（如枪支、军用或警用械具（含主要零部件）及其仿制品，爆炸物品，管制刀具，易燃易爆物品等）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>托运人/托运人代理人检查结果【货物/邮件无隐含性危险品及航空禁运限运物品】
-                                                                      检查人：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>陈晶晶</t>
-    </r>
+    <t>托运人/托运人代理人检查结果【货物/邮件无隐含性危险品及航空禁运限运物品】
+                                                                      检查人：陈晶晶</t>
   </si>
   <si>
     <r>
@@ -281,7 +209,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,13 +224,11 @@
     </font>
     <font>
       <sz val="16"/>
-      <color theme="1"/>
       <name val="黑体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
-      <color theme="1"/>
       <name val="黑体"/>
       <charset val="134"/>
     </font>
@@ -314,27 +240,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -353,7 +269,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -513,17 +430,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1152,137 +1058,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="29" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="28" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="30" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="31" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="32" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1310,133 +1216,109 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="6" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="15" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="16" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="17" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="10" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="19" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1445,7 +1327,7 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="11" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
@@ -1454,7 +1336,7 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="20" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="21" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1">
@@ -1514,10 +1396,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
   </cellXfs>
@@ -1951,348 +1833,348 @@
       <c r="X3" s="8"/>
     </row>
     <row r="4" s="1" customFormat="1" ht="28" customHeight="1" spans="1:24">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="10" t="s">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="11" t="s">
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="10" t="s">
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
+      <c r="L4" s="9"/>
+      <c r="M4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
-      <c r="Q4" s="11" t="s">
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12"/>
-      <c r="W4" s="12"/>
-      <c r="X4" s="12"/>
+      <c r="R4" s="9"/>
+      <c r="S4" s="9"/>
+      <c r="T4" s="9"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="35.15" customHeight="1" spans="1:24">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9" t="s">
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9" t="s">
+      <c r="F5" s="8"/>
+      <c r="G5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9" t="s">
+      <c r="H5" s="8"/>
+      <c r="I5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="13" t="s">
+      <c r="J5" s="8"/>
+      <c r="K5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="16" t="s">
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="17" t="s">
+      <c r="P5" s="7"/>
+      <c r="Q5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="R5" s="18"/>
-      <c r="S5" s="18"/>
-      <c r="T5" s="19"/>
-      <c r="U5" s="20" t="s">
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="V5" s="21"/>
-      <c r="W5" s="21"/>
-      <c r="X5" s="22"/>
+      <c r="V5" s="18"/>
+      <c r="W5" s="18"/>
+      <c r="X5" s="19"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="21" customHeight="1" spans="1:24">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="23" t="s">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="24"/>
-      <c r="R6" s="25"/>
-      <c r="S6" s="25"/>
-      <c r="T6" s="26"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="28"/>
-      <c r="W6" s="28"/>
-      <c r="X6" s="29"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="15"/>
+      <c r="S6" s="15"/>
+      <c r="T6" s="16"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="21"/>
+      <c r="W6" s="21"/>
+      <c r="X6" s="22"/>
     </row>
     <row r="7" s="1" customFormat="1" ht="57" customHeight="1" spans="1:24">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="9" t="s">
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="16" t="s">
+      <c r="F7" s="8"/>
+      <c r="G7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="16"/>
-      <c r="I7" s="13" t="s">
+      <c r="H7" s="7"/>
+      <c r="I7" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="J7" s="15"/>
-      <c r="K7" s="13" t="s">
+      <c r="J7" s="13"/>
+      <c r="K7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="15"/>
-      <c r="P7" s="13" t="s">
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="Q7" s="14"/>
-      <c r="R7" s="14"/>
-      <c r="S7" s="14"/>
-      <c r="T7" s="15"/>
-      <c r="U7" s="9" t="s">
+      <c r="Q7" s="12"/>
+      <c r="R7" s="12"/>
+      <c r="S7" s="12"/>
+      <c r="T7" s="13"/>
+      <c r="U7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
     </row>
     <row r="8" s="1" customFormat="1" ht="23" customHeight="1" spans="1:24">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8">
         <v>110</v>
       </c>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23">
+      <c r="F8" s="8"/>
+      <c r="G8" s="8">
         <v>400</v>
       </c>
-      <c r="H8" s="23"/>
-      <c r="I8" s="24">
+      <c r="H8" s="8"/>
+      <c r="I8" s="14">
         <v>400</v>
       </c>
-      <c r="J8" s="26"/>
-      <c r="K8" s="31" t="s">
+      <c r="J8" s="16"/>
+      <c r="K8" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="32"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="24" t="s">
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="25"/>
-      <c r="S8" s="25"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="23"/>
-      <c r="W8" s="23"/>
-      <c r="X8" s="23"/>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="15"/>
+      <c r="S8" s="15"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
     </row>
     <row r="9" s="1" customFormat="1" ht="23" customHeight="1" spans="1:24">
-      <c r="A9" s="23"/>
-      <c r="B9" s="23"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="26"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
-      <c r="S9" s="25"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="23"/>
-      <c r="V9" s="23"/>
-      <c r="W9" s="23"/>
-      <c r="X9" s="23"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="14"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+      <c r="S9" s="15"/>
+      <c r="T9" s="16"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
     </row>
     <row r="10" s="1" customFormat="1" ht="23" customHeight="1" spans="1:24">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="35"/>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
-      <c r="S10" s="25"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="23"/>
-      <c r="V10" s="23"/>
-      <c r="W10" s="23"/>
-      <c r="X10" s="23"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="27"/>
+      <c r="M10" s="27"/>
+      <c r="N10" s="27"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="14"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="16"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
     </row>
     <row r="11" s="1" customFormat="1" ht="23" customHeight="1" spans="1:24">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="35"/>
-      <c r="M11" s="35"/>
-      <c r="N11" s="35"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
-      <c r="S11" s="25"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="23"/>
-      <c r="V11" s="23"/>
-      <c r="W11" s="23"/>
-      <c r="X11" s="23"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="27"/>
+      <c r="M11" s="27"/>
+      <c r="N11" s="27"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="14"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="15"/>
+      <c r="T11" s="16"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
     </row>
     <row r="12" s="1" customFormat="1" ht="23" customHeight="1" spans="1:24">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="35"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="35"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="25"/>
-      <c r="S12" s="25"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="23"/>
-      <c r="V12" s="23"/>
-      <c r="W12" s="23"/>
-      <c r="X12" s="23"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="27"/>
+      <c r="M12" s="27"/>
+      <c r="N12" s="27"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
     </row>
     <row r="13" s="1" customFormat="1" ht="23" customHeight="1" spans="1:24">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="37"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="39"/>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="25"/>
-      <c r="R13" s="25"/>
-      <c r="S13" s="25"/>
-      <c r="T13" s="26"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="23"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8"/>
     </row>
     <row r="14" s="1" customFormat="1" ht="71" customHeight="1" spans="1:24">
-      <c r="A14" s="9" t="s">
+      <c r="A14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="40" t="s">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="40"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="40"/>
-      <c r="R14" s="40"/>
-      <c r="S14" s="40"/>
-      <c r="T14" s="40"/>
-      <c r="U14" s="40"/>
-      <c r="V14" s="40"/>
-      <c r="W14" s="40"/>
-      <c r="X14" s="40"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="32"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="32"/>
+      <c r="O14" s="32"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="32"/>
+      <c r="R14" s="32"/>
+      <c r="S14" s="32"/>
+      <c r="T14" s="32"/>
+      <c r="U14" s="32"/>
+      <c r="V14" s="32"/>
+      <c r="W14" s="32"/>
+      <c r="X14" s="32"/>
     </row>
     <row r="15" s="1" customFormat="1" ht="41" customHeight="1" spans="1:24">
       <c r="A15" s="7" t="s">
@@ -2301,355 +2183,355 @@
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="23" t="s">
+      <c r="E15" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
-      <c r="O15" s="23"/>
-      <c r="P15" s="23"/>
-      <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
-      <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
-      <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="23"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="8"/>
+      <c r="Q15" s="8"/>
+      <c r="R15" s="8"/>
+      <c r="S15" s="8"/>
+      <c r="T15" s="8"/>
+      <c r="U15" s="8"/>
+      <c r="V15" s="8"/>
+      <c r="W15" s="8"/>
+      <c r="X15" s="8"/>
     </row>
     <row r="16" s="1" customFormat="1" ht="15" customHeight="1"/>
     <row r="17" s="2" customFormat="1" ht="24.95" customHeight="1" spans="1:24">
-      <c r="A17" s="41" t="s">
+      <c r="A17" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="41"/>
-      <c r="M17" s="41"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="41"/>
-      <c r="S17" s="41" t="s">
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
+      <c r="S17" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="T17" s="41"/>
-      <c r="U17" s="42"/>
-      <c r="V17" s="43" t="s">
+      <c r="T17" s="33"/>
+      <c r="U17" s="34"/>
+      <c r="V17" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="W17" s="44"/>
-      <c r="X17" s="45"/>
+      <c r="W17" s="36"/>
+      <c r="X17" s="37"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="24.95" customHeight="1" spans="1:24">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="46"/>
-      <c r="O18" s="46"/>
-      <c r="P18" s="46"/>
-      <c r="Q18" s="46"/>
-      <c r="R18" s="46"/>
-      <c r="S18" s="47" t="s">
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="38"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="38"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="38"/>
+      <c r="R18" s="38"/>
+      <c r="S18" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="T18" s="47" t="s">
+      <c r="T18" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="U18" s="48" t="s">
+      <c r="U18" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="V18" s="49" t="s">
+      <c r="V18" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="W18" s="50" t="s">
+      <c r="W18" s="42" t="s">
         <v>36</v>
       </c>
-      <c r="X18" s="51" t="s">
+      <c r="X18" s="43" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="27" customHeight="1" spans="1:24">
-      <c r="A19" s="52">
+      <c r="A19" s="44">
         <v>1</v>
       </c>
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="53"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="53"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="53"/>
-      <c r="L19" s="53"/>
-      <c r="M19" s="53"/>
-      <c r="N19" s="53"/>
-      <c r="O19" s="53"/>
-      <c r="P19" s="53"/>
-      <c r="Q19" s="53"/>
-      <c r="R19" s="53"/>
-      <c r="S19" s="54" t="s">
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="45"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="45"/>
+      <c r="O19" s="45"/>
+      <c r="P19" s="45"/>
+      <c r="Q19" s="45"/>
+      <c r="R19" s="45"/>
+      <c r="S19" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="T19" s="55"/>
-      <c r="U19" s="56"/>
-      <c r="V19" s="57"/>
-      <c r="W19" s="55"/>
-      <c r="X19" s="58"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="49"/>
+      <c r="W19" s="47"/>
+      <c r="X19" s="50"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="27" customHeight="1" spans="1:24">
-      <c r="A20" s="52">
+      <c r="A20" s="44">
         <v>2</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="B20" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="53"/>
-      <c r="D20" s="53"/>
-      <c r="E20" s="53"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="53"/>
-      <c r="H20" s="53"/>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="53"/>
-      <c r="L20" s="53"/>
-      <c r="M20" s="53"/>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
-      <c r="P20" s="53"/>
-      <c r="Q20" s="53"/>
-      <c r="R20" s="53"/>
-      <c r="S20" s="54" t="s">
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
+      <c r="H20" s="45"/>
+      <c r="I20" s="45"/>
+      <c r="J20" s="45"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="45"/>
+      <c r="M20" s="45"/>
+      <c r="N20" s="45"/>
+      <c r="O20" s="45"/>
+      <c r="P20" s="45"/>
+      <c r="Q20" s="45"/>
+      <c r="R20" s="45"/>
+      <c r="S20" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="T20" s="55"/>
-      <c r="U20" s="56"/>
-      <c r="V20" s="57"/>
-      <c r="W20" s="55"/>
-      <c r="X20" s="58"/>
+      <c r="T20" s="47"/>
+      <c r="U20" s="48"/>
+      <c r="V20" s="49"/>
+      <c r="W20" s="47"/>
+      <c r="X20" s="50"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="27" customHeight="1" spans="1:24">
-      <c r="A21" s="52">
+      <c r="A21" s="44">
         <v>3</v>
       </c>
-      <c r="B21" s="53" t="s">
+      <c r="B21" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
-      <c r="Q21" s="53"/>
-      <c r="R21" s="53"/>
-      <c r="S21" s="54" t="s">
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="45"/>
+      <c r="M21" s="45"/>
+      <c r="N21" s="45"/>
+      <c r="O21" s="45"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="45"/>
+      <c r="R21" s="45"/>
+      <c r="S21" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="T21" s="55"/>
-      <c r="U21" s="56"/>
-      <c r="V21" s="57"/>
-      <c r="W21" s="55"/>
-      <c r="X21" s="58"/>
+      <c r="T21" s="47"/>
+      <c r="U21" s="48"/>
+      <c r="V21" s="49"/>
+      <c r="W21" s="47"/>
+      <c r="X21" s="50"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="27" customHeight="1" spans="1:24">
-      <c r="A22" s="59">
+      <c r="A22" s="51">
         <v>4</v>
       </c>
-      <c r="B22" s="60" t="s">
+      <c r="B22" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="60"/>
-      <c r="E22" s="60"/>
-      <c r="F22" s="60"/>
-      <c r="G22" s="60"/>
-      <c r="H22" s="60"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="60"/>
-      <c r="M22" s="60"/>
-      <c r="N22" s="60"/>
-      <c r="O22" s="60"/>
-      <c r="P22" s="60"/>
-      <c r="Q22" s="60"/>
-      <c r="R22" s="60"/>
-      <c r="S22" s="54" t="s">
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="52"/>
+      <c r="J22" s="52"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="52"/>
+      <c r="M22" s="52"/>
+      <c r="N22" s="52"/>
+      <c r="O22" s="52"/>
+      <c r="P22" s="52"/>
+      <c r="Q22" s="52"/>
+      <c r="R22" s="52"/>
+      <c r="S22" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="T22" s="61"/>
-      <c r="U22" s="62"/>
-      <c r="V22" s="63"/>
-      <c r="W22" s="61"/>
-      <c r="X22" s="64"/>
+      <c r="T22" s="53"/>
+      <c r="U22" s="54"/>
+      <c r="V22" s="55"/>
+      <c r="W22" s="53"/>
+      <c r="X22" s="56"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="27" customHeight="1" spans="1:24">
-      <c r="A23" s="59">
+      <c r="A23" s="51">
         <v>5</v>
       </c>
-      <c r="B23" s="60" t="s">
+      <c r="B23" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="60"/>
-      <c r="D23" s="60"/>
-      <c r="E23" s="60"/>
-      <c r="F23" s="60"/>
-      <c r="G23" s="60"/>
-      <c r="H23" s="60"/>
-      <c r="I23" s="60"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="60"/>
-      <c r="M23" s="60"/>
-      <c r="N23" s="60"/>
-      <c r="O23" s="60"/>
-      <c r="P23" s="60"/>
-      <c r="Q23" s="60"/>
-      <c r="R23" s="60"/>
-      <c r="S23" s="54" t="s">
+      <c r="C23" s="52"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="52"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="52"/>
+      <c r="I23" s="52"/>
+      <c r="J23" s="52"/>
+      <c r="K23" s="52"/>
+      <c r="L23" s="52"/>
+      <c r="M23" s="52"/>
+      <c r="N23" s="52"/>
+      <c r="O23" s="52"/>
+      <c r="P23" s="52"/>
+      <c r="Q23" s="52"/>
+      <c r="R23" s="52"/>
+      <c r="S23" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="T23" s="61"/>
-      <c r="U23" s="62"/>
-      <c r="V23" s="63"/>
-      <c r="W23" s="61"/>
-      <c r="X23" s="64"/>
+      <c r="T23" s="53"/>
+      <c r="U23" s="54"/>
+      <c r="V23" s="55"/>
+      <c r="W23" s="53"/>
+      <c r="X23" s="56"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="34" customHeight="1" spans="1:24">
-      <c r="A24" s="65">
+      <c r="A24" s="57">
         <v>6</v>
       </c>
-      <c r="B24" s="66" t="s">
+      <c r="B24" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="66"/>
-      <c r="G24" s="66"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="66"/>
-      <c r="J24" s="66"/>
-      <c r="K24" s="66"/>
-      <c r="L24" s="66"/>
-      <c r="M24" s="66"/>
-      <c r="N24" s="66"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66"/>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="54" t="s">
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="58"/>
+      <c r="M24" s="58"/>
+      <c r="N24" s="58"/>
+      <c r="O24" s="58"/>
+      <c r="P24" s="58"/>
+      <c r="Q24" s="58"/>
+      <c r="R24" s="58"/>
+      <c r="S24" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="T24" s="67"/>
-      <c r="U24" s="68"/>
-      <c r="V24" s="69"/>
-      <c r="W24" s="70"/>
-      <c r="X24" s="71"/>
+      <c r="T24" s="59"/>
+      <c r="U24" s="60"/>
+      <c r="V24" s="61"/>
+      <c r="W24" s="62"/>
+      <c r="X24" s="63"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="41" customHeight="1" spans="1:24">
-      <c r="A25" s="72" t="s">
+      <c r="A25" s="64" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="73"/>
-      <c r="C25" s="73"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="73"/>
-      <c r="J25" s="73"/>
-      <c r="K25" s="73"/>
-      <c r="L25" s="73"/>
-      <c r="M25" s="73"/>
-      <c r="N25" s="73"/>
-      <c r="O25" s="73"/>
-      <c r="P25" s="73"/>
-      <c r="Q25" s="73"/>
-      <c r="R25" s="73"/>
-      <c r="S25" s="73"/>
-      <c r="T25" s="73"/>
-      <c r="U25" s="73"/>
-      <c r="V25" s="74"/>
-      <c r="W25" s="74"/>
-      <c r="X25" s="74"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="65"/>
+      <c r="D25" s="65"/>
+      <c r="E25" s="65"/>
+      <c r="F25" s="65"/>
+      <c r="G25" s="65"/>
+      <c r="H25" s="65"/>
+      <c r="I25" s="65"/>
+      <c r="J25" s="65"/>
+      <c r="K25" s="65"/>
+      <c r="L25" s="65"/>
+      <c r="M25" s="65"/>
+      <c r="N25" s="65"/>
+      <c r="O25" s="65"/>
+      <c r="P25" s="65"/>
+      <c r="Q25" s="65"/>
+      <c r="R25" s="65"/>
+      <c r="S25" s="65"/>
+      <c r="T25" s="65"/>
+      <c r="U25" s="65"/>
+      <c r="V25" s="66"/>
+      <c r="W25" s="66"/>
+      <c r="X25" s="66"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="41" customHeight="1" spans="1:24">
-      <c r="A26" s="75" t="s">
+      <c r="A26" s="67" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="76"/>
-      <c r="C26" s="76"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
-      <c r="I26" s="76"/>
-      <c r="J26" s="76"/>
-      <c r="K26" s="76"/>
-      <c r="L26" s="76"/>
-      <c r="M26" s="76"/>
-      <c r="N26" s="76"/>
-      <c r="O26" s="76"/>
-      <c r="P26" s="76"/>
-      <c r="Q26" s="76"/>
-      <c r="R26" s="76"/>
-      <c r="S26" s="76"/>
-      <c r="T26" s="76"/>
-      <c r="U26" s="76"/>
-      <c r="V26" s="76"/>
-      <c r="W26" s="76"/>
-      <c r="X26" s="76"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="68"/>
+      <c r="J26" s="68"/>
+      <c r="K26" s="68"/>
+      <c r="L26" s="68"/>
+      <c r="M26" s="68"/>
+      <c r="N26" s="68"/>
+      <c r="O26" s="68"/>
+      <c r="P26" s="68"/>
+      <c r="Q26" s="68"/>
+      <c r="R26" s="68"/>
+      <c r="S26" s="68"/>
+      <c r="T26" s="68"/>
+      <c r="U26" s="68"/>
+      <c r="V26" s="68"/>
+      <c r="W26" s="68"/>
+      <c r="X26" s="68"/>
     </row>
     <row r="27" s="3" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A27" s="77"/>
+      <c r="A27" s="69"/>
     </row>
     <row r="28" s="3" customFormat="1" ht="24" customHeight="1" spans="1:24">
-      <c r="A28" s="78"/>
+      <c r="A28" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="85">
@@ -2742,6 +2624,5 @@
   <pageMargins left="0.275" right="0.196527777777778" top="0.236111111111111" bottom="0.236111111111111" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>